--- a/Team-Data/2007-08/1-28-2007-08.xlsx
+++ b/Team-Data/2007-08/1-28-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -754,7 +821,7 @@
         <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
@@ -808,7 +875,7 @@
         <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>23</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -942,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL3" t="n">
         <v>9</v>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.386</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,40 +1110,40 @@
         <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79</v>
+        <v>79.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L4" t="n">
         <v>6.2</v>
       </c>
       <c r="M4" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O4" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P4" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.707</v>
+        <v>0.706</v>
       </c>
       <c r="R4" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T4" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="U4" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="V4" t="n">
         <v>15.3</v>
@@ -1088,31 +1155,31 @@
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA4" t="n">
         <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
         <v>4</v>
@@ -1124,7 +1191,7 @@
         <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1133,19 +1200,19 @@
         <v>16</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
         <v>23</v>
@@ -1154,19 +1221,19 @@
         <v>27</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV4" t="n">
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
       </c>
       <c r="AY4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
@@ -1175,7 +1242,7 @@
         <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
         <v>6</v>
@@ -1324,7 +1391,7 @@
         <v>23</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1348,7 +1415,7 @@
         <v>15</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
         <v>14</v>
@@ -1357,7 +1424,7 @@
         <v>17</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1503,7 +1570,7 @@
         <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>24</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -1571,58 +1638,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.705</v>
+        <v>0.698</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J7" t="n">
         <v>78.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.472</v>
+        <v>0.47</v>
       </c>
       <c r="L7" t="n">
         <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O7" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="P7" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0.822</v>
       </c>
       <c r="R7" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T7" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U7" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V7" t="n">
         <v>13</v>
@@ -1640,25 +1707,25 @@
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB7" t="n">
         <v>101.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
         <v>3</v>
       </c>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
@@ -1670,10 +1737,10 @@
         <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM7" t="n">
         <v>20</v>
@@ -1694,10 +1761,10 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
         <v>22</v>
@@ -1721,10 +1788,10 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC7" t="n">
         <v>8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="n">
         <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.591</v>
+        <v>0.605</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.451</v>
@@ -1780,40 +1847,40 @@
         <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="O8" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="P8" t="n">
-        <v>30.9</v>
+        <v>31.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S8" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T8" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y8" t="n">
         <v>5</v>
@@ -1825,25 +1892,25 @@
         <v>24.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.1</v>
+        <v>106.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
         <v>10</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>11</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1852,7 +1919,7 @@
         <v>5</v>
       </c>
       <c r="AK8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
         <v>17</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1876,16 +1943,16 @@
         <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>7.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
         <v>3</v>
@@ -2025,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
         <v>15</v>
@@ -2049,7 +2116,7 @@
         <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
         <v>12</v>
@@ -2061,7 +2128,7 @@
         <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -2201,10 +2268,10 @@
         <v>8</v>
       </c>
       <c r="AF10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
@@ -2234,7 +2301,7 @@
         <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
         <v>7</v>
@@ -2252,7 +2319,7 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
@@ -2389,7 +2456,7 @@
         <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>18</v>
@@ -2407,7 +2474,7 @@
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
         <v>27</v>
@@ -2449,7 +2516,7 @@
         <v>22</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
         <v>12</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
         <v>2</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>16</v>
@@ -2604,7 +2671,7 @@
         <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>4</v>
@@ -2628,7 +2695,7 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -2663,91 +2730,91 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="n">
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>0.317</v>
+        <v>0.325</v>
       </c>
       <c r="H13" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J13" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.438</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.335</v>
       </c>
       <c r="O13" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="P13" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R13" t="n">
         <v>9.6</v>
       </c>
       <c r="S13" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T13" t="n">
-        <v>41.1</v>
+        <v>41.4</v>
       </c>
       <c r="U13" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="V13" t="n">
         <v>14.7</v>
       </c>
       <c r="W13" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z13" t="n">
         <v>21.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.7</v>
+        <v>-4.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>26</v>
@@ -2756,22 +2823,22 @@
         <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ13" t="n">
         <v>19</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>9</v>
@@ -2786,13 +2853,13 @@
         <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
@@ -2801,7 +2868,7 @@
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
         <v>20</v>
@@ -2810,10 +2877,10 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
         <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>7</v>
@@ -2962,10 +3029,10 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2986,7 +3053,7 @@
         <v>12</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
         <v>18</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -3027,61 +3094,61 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.289</v>
+        <v>0.295</v>
       </c>
       <c r="H15" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L15" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O15" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P15" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.748</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S15" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T15" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U15" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="W15" t="n">
         <v>5.8</v>
@@ -3090,22 +3157,22 @@
         <v>5.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>101</v>
+        <v>101.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.4</v>
+        <v>-4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,10 +3184,10 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI15" t="n">
         <v>8</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>9</v>
       </c>
       <c r="AJ15" t="n">
         <v>14</v>
@@ -3141,10 +3208,10 @@
         <v>15</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
         <v>23</v>
@@ -3159,25 +3226,25 @@
         <v>21</v>
       </c>
       <c r="AV15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW15" t="n">
         <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>4</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>28</v>
@@ -3326,7 +3393,7 @@
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3548,7 @@
         <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
         <v>16</v>
@@ -3502,7 +3569,7 @@
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
         <v>24</v>
@@ -3520,7 +3587,7 @@
         <v>26</v>
       </c>
       <c r="AU17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AV17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3684,7 +3751,7 @@
         <v>19</v>
       </c>
       <c r="AO18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
@@ -3863,13 +3930,13 @@
         <v>17</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>27</v>
@@ -3887,7 +3954,7 @@
         <v>4</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
         <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>0.727</v>
+        <v>0.721</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
         <v>20.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O20" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P20" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.782</v>
+        <v>0.78</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U20" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
         <v>4</v>
@@ -4003,22 +4070,22 @@
         <v>4.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF20" t="n">
         <v>2</v>
@@ -4027,16 +4094,16 @@
         <v>2</v>
       </c>
       <c r="AH20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
         <v>7</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4048,7 +4115,7 @@
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP20" t="n">
         <v>30</v>
@@ -4057,7 +4124,7 @@
         <v>6</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS20" t="n">
         <v>13</v>
@@ -4066,19 +4133,19 @@
         <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>2</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4227,7 +4294,7 @@
         <v>17</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO21" t="n">
         <v>14</v>
@@ -4269,7 +4336,7 @@
         <v>15</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4452,7 @@
         <v>6</v>
       </c>
       <c r="AF22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG22" t="n">
         <v>8</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -4564,10 +4631,10 @@
         <v>2</v>
       </c>
       <c r="AE23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
         <v>24</v>
@@ -4609,7 +4676,7 @@
         <v>29</v>
       </c>
       <c r="AT23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>0.8</v>
       </c>
       <c r="AD25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE25" t="n">
         <v>10</v>
       </c>
-      <c r="AE25" t="n">
-        <v>11</v>
-      </c>
       <c r="AF25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
@@ -4967,7 +5034,7 @@
         <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
         <v>20</v>
@@ -4976,7 +5043,7 @@
         <v>28</v>
       </c>
       <c r="AU25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E27" t="n">
         <v>28</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>0.651</v>
+        <v>0.667</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L27" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M27" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.375</v>
+        <v>0.377</v>
       </c>
       <c r="O27" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="P27" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.753</v>
+        <v>0.749</v>
       </c>
       <c r="R27" t="n">
         <v>10.1</v>
       </c>
       <c r="S27" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T27" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U27" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="V27" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.7</v>
@@ -5274,22 +5341,22 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>6</v>
@@ -5301,7 +5368,7 @@
         <v>6</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5310,7 +5377,7 @@
         <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AL27" t="n">
         <v>6</v>
@@ -5322,13 +5389,13 @@
         <v>5</v>
       </c>
       <c r="AO27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP27" t="n">
         <v>26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AR27" t="n">
         <v>22</v>
@@ -5337,10 +5404,10 @@
         <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5349,7 +5416,7 @@
         <v>23</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>13</v>
@@ -5364,7 +5431,7 @@
         <v>18</v>
       </c>
       <c r="BC27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
@@ -5483,28 +5550,28 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
         <v>3</v>
       </c>
       <c r="AK28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN28" t="n">
         <v>26</v>
       </c>
-      <c r="AM28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>25</v>
-      </c>
       <c r="AO28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
@@ -5519,13 +5586,13 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="n">
         <v>19</v>
       </c>
       <c r="AV28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW28" t="n">
         <v>24</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
@@ -5701,7 +5768,7 @@
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
@@ -5716,7 +5783,7 @@
         <v>25</v>
       </c>
       <c r="AY29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6</v>
+        <v>0.591</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,7 +5842,7 @@
         <v>39.7</v>
       </c>
       <c r="J30" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.493</v>
@@ -5790,37 +5857,37 @@
         <v>0.361</v>
       </c>
       <c r="O30" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="P30" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0.752</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
         <v>29.1</v>
       </c>
       <c r="T30" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U30" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="V30" t="n">
         <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
         <v>24.8</v>
@@ -5829,22 +5896,22 @@
         <v>23.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.3</v>
+        <v>105.5</v>
       </c>
       <c r="AC30" t="n">
         <v>5.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5865,7 +5932,7 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,16 +5941,16 @@
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS30" t="n">
         <v>28</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5892,7 +5959,7 @@
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6038,7 +6105,7 @@
         <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL31" t="n">
         <v>12</v>
@@ -6080,7 +6147,7 @@
         <v>12</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
@@ -6089,7 +6156,7 @@
         <v>27</v>
       </c>
       <c r="BB31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-28-2007-08</t>
+          <t>2008-01-28</t>
         </is>
       </c>
     </row>
